--- a/ig/ch-elm/ch-elm-results-geno-to-component-interpretation-code.xlsx
+++ b/ig/ch-elm/ch-elm-results-geno-to-component-interpretation-code.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.13.1</t>
+    <t>1.14.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-01-21T11:21:00+00:00</t>
+    <t>2026-05-26T14:58:40+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/ch-elm/ch-elm-results-geno-to-component-interpretation-code.xlsx
+++ b/ig/ch-elm/ch-elm-results-geno-to-component-interpretation-code.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.14.0</t>
+    <t>1.14.1</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-26T14:58:40+00:00</t>
+    <t>2026-07-01T19:23:08+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/ch-elm/ch-elm-results-geno-to-component-interpretation-code.xlsx
+++ b/ig/ch-elm/ch-elm-results-geno-to-component-interpretation-code.xlsx
@@ -8,12 +8,13 @@
   <sheets>
     <sheet name="Metadata" r:id="rId3" sheetId="1"/>
     <sheet name="Mapping Table 0" r:id="rId4" sheetId="2"/>
+    <sheet name="Mapping Table 1" r:id="rId5" sheetId="3"/>
   </sheets>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="45" uniqueCount="40">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="239" uniqueCount="134">
   <si>
     <t>Property</t>
   </si>
@@ -30,7 +31,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.14.1</t>
+    <t>1.15.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +61,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-01T19:23:08+00:00</t>
+    <t>2026-08-12T07:20:00+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -114,22 +115,304 @@
     <t>Relationship</t>
   </si>
   <si>
+    <t>http://snomed.info/sct</t>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t>http://fhir.ch/ig/ch-elm/CodeSystem/ch-elm-interpretation-codes-vs</t>
+  </si>
+  <si>
+    <t>1087501000112108</t>
+  </si>
+  <si>
+    <t>Carbapenemase-producing Buttiauxella</t>
+  </si>
+  <si>
+    <t>related-to</t>
+  </si>
+  <si>
+    <t>http://fhir.ch/ig/ch-elm/ValueSet/ch-elm-interpretation-codes-pos</t>
+  </si>
+  <si>
+    <t>1089101000112105</t>
+  </si>
+  <si>
+    <t>Carbapenemase-producing Citrobacter amalonaticus</t>
+  </si>
+  <si>
+    <t>1089301000112107</t>
+  </si>
+  <si>
+    <t>Carbapenemase-producing Citrobacter braakii</t>
+  </si>
+  <si>
+    <t>1089501000112101</t>
+  </si>
+  <si>
+    <t>Carbapenemase-producing Citrobacter</t>
+  </si>
+  <si>
+    <t>1089701000112106</t>
+  </si>
+  <si>
+    <t>Carbapenemase-producing Citrobacter farmeri</t>
+  </si>
+  <si>
+    <t>1089901000112108</t>
+  </si>
+  <si>
+    <t>Carbapenemase-producing Citrobacter freundii</t>
+  </si>
+  <si>
+    <t>1090201000112105</t>
+  </si>
+  <si>
+    <t>Carbapenemase-producing Citrobacter gillenii</t>
+  </si>
+  <si>
+    <t>1090401000112109</t>
+  </si>
+  <si>
+    <t>Carbapenemase-producing Citrobacter koseri</t>
+  </si>
+  <si>
+    <t>1090601000112107</t>
+  </si>
+  <si>
+    <t>Carbapenemase-producing Citrobacter murliniae</t>
+  </si>
+  <si>
+    <t>1091001000112109</t>
+  </si>
+  <si>
+    <t>Carbapenemase-producing Citrobacter sedlakii</t>
+  </si>
+  <si>
+    <t>1091201000112104</t>
+  </si>
+  <si>
+    <t>Carbapenemase-producing Citrobacter werkmanii</t>
+  </si>
+  <si>
+    <t>1091401000112100</t>
+  </si>
+  <si>
+    <t>Carbapenemase-producing Citrobacter youngae</t>
+  </si>
+  <si>
+    <t>1092401000112105</t>
+  </si>
+  <si>
+    <t>Carbapenemase-producing Cronobacter sakazakii</t>
+  </si>
+  <si>
+    <t>1093401000112101</t>
+  </si>
+  <si>
+    <t>Carbapenemase-producing Enterobacter</t>
+  </si>
+  <si>
+    <t>1093601000112103</t>
+  </si>
+  <si>
+    <t>Carbapenemase-producing Enterobacter asburiae</t>
+  </si>
+  <si>
+    <t>1094301000112105</t>
+  </si>
+  <si>
+    <t>Carbapenemase-producing Enterobacter hormaechei</t>
+  </si>
+  <si>
+    <t>1096801000112108</t>
+  </si>
+  <si>
+    <t>Carbapenemase-producing Klebsiella</t>
+  </si>
+  <si>
+    <t>1097701000112102</t>
+  </si>
+  <si>
+    <t>Carbapenemase-producing Klebsiella pneumoniae subsp. ozaenae</t>
+  </si>
+  <si>
+    <t>1098201000112108</t>
+  </si>
+  <si>
+    <t>Carbapenemase-producing Klebsiella pneumoniae</t>
+  </si>
+  <si>
+    <t>1099001000112108</t>
+  </si>
+  <si>
+    <t>Carbapenemase-producing Kluyvera</t>
+  </si>
+  <si>
+    <t>1099201000112103</t>
+  </si>
+  <si>
+    <t>Carbapenemase-producing Kluyvera ascorbata</t>
+  </si>
+  <si>
+    <t>1099401000112104</t>
+  </si>
+  <si>
+    <t>Carbapenemase-producing Kluyvera cryocrescens</t>
+  </si>
+  <si>
+    <t>1099601000112101</t>
+  </si>
+  <si>
+    <t>Carbapenemase-producing Kluyvera georgiana</t>
+  </si>
+  <si>
+    <t>1099801000112102</t>
+  </si>
+  <si>
+    <t>Carbapenemase-producing Kluyvera intermedia</t>
+  </si>
+  <si>
+    <t>1100001000112108</t>
+  </si>
+  <si>
+    <t>Carbapenemase-producing Leclercia</t>
+  </si>
+  <si>
+    <t>1100201000112103</t>
+  </si>
+  <si>
+    <t>Carbapenemase-producing Leclercia adecarboxylata</t>
+  </si>
+  <si>
+    <t>1105401000112106</t>
+  </si>
+  <si>
+    <t>Carbapenemase-producing Raoultella ornithinolytica</t>
+  </si>
+  <si>
+    <t>1105601000112109</t>
+  </si>
+  <si>
+    <t>Carbapenemase-producing Raoultella planticola</t>
+  </si>
+  <si>
+    <t>1105801000112108</t>
+  </si>
+  <si>
+    <t>Carbapenemase-producing Raoultella terrigena</t>
+  </si>
+  <si>
+    <t>1106001000112106</t>
+  </si>
+  <si>
+    <t>Carbapenemase-producing Salmonella</t>
+  </si>
+  <si>
+    <t>1108301000112108</t>
+  </si>
+  <si>
+    <t>Carbapenemase-producing Shigella</t>
+  </si>
+  <si>
+    <t>1112101000112106</t>
+  </si>
+  <si>
+    <t>Carbapenemase-producing Lelliottia amnigena</t>
+  </si>
+  <si>
+    <t>1359810002</t>
+  </si>
+  <si>
+    <t>Carbapenemase-producing Cronobacter</t>
+  </si>
+  <si>
+    <t>1359811003</t>
+  </si>
+  <si>
+    <t>Carbapenemase-producing Escherichia spp</t>
+  </si>
+  <si>
+    <t>1362138006</t>
+  </si>
+  <si>
+    <t>Carbapenemase-producing Lelliottia</t>
+  </si>
+  <si>
+    <t>1388125003</t>
+  </si>
+  <si>
+    <t>Carbapenemase-producing Pluralibacter (organism)</t>
+  </si>
+  <si>
+    <t>308241000087107</t>
+  </si>
+  <si>
+    <t>Carbapenemase-producing Pluralibacter gergoviae (organism)</t>
+  </si>
+  <si>
+    <t>33691000087101</t>
+  </si>
+  <si>
+    <t>Carbapenemase-producing Klebsiella variicola</t>
+  </si>
+  <si>
+    <t>432763001</t>
+  </si>
+  <si>
+    <t>Enterobacter ludwigii (organism)</t>
+  </si>
+  <si>
+    <t>44601000087107</t>
+  </si>
+  <si>
+    <t>Carbapenemase-producing Citrobacter freundii complex</t>
+  </si>
+  <si>
+    <t>51271000087100</t>
+  </si>
+  <si>
+    <t>Carbapenemase-producing Klebsiella oxytoca</t>
+  </si>
+  <si>
+    <t>734352006</t>
+  </si>
+  <si>
+    <t>Carbapenemase-producing Klebsiella aerogenes (organism)</t>
+  </si>
+  <si>
+    <t>734353001</t>
+  </si>
+  <si>
+    <t>Carbapenemase-producing Enterobacter cloacae complex (organism)</t>
+  </si>
+  <si>
+    <t>737528008</t>
+  </si>
+  <si>
+    <t>Carbapenemase-producing Escherichia coli (organism)</t>
+  </si>
+  <si>
+    <t>737529000</t>
+  </si>
+  <si>
+    <t>Carbapenemase-producing Enterobacter cloacae (organism)</t>
+  </si>
+  <si>
+    <t>770392005</t>
+  </si>
+  <si>
+    <t>Carbapenemase-producing Raoultella (organism)</t>
+  </si>
+  <si>
     <t>http://loinc.org</t>
   </si>
   <si>
-    <t/>
-  </si>
-  <si>
-    <t>http://fhir.ch/ig/ch-elm/CodeSystem/ch-elm-interpretation-codes-vs</t>
-  </si>
-  <si>
     <t>94053-6</t>
   </si>
   <si>
     <t>Mycobacterium tuberculosis complex resistance panel by Molecular genetics method</t>
-  </si>
-  <si>
-    <t>related-to</t>
   </si>
   <si>
     <t>http://fhir.ch/ig/ch-elm/ValueSet/ch-elm-interpretation-codes-pos-neg</t>
@@ -406,6 +689,740 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <dimension ref="A1:E48"/>
+  <sheetFormatPr defaultRowHeight="15.0"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="s" s="1">
+        <v>27</v>
+      </c>
+      <c r="B1" t="s" s="1">
+        <v>31</v>
+      </c>
+      <c r="C1" t="s" s="1">
+        <v>32</v>
+      </c>
+      <c r="D1" t="s" s="1">
+        <v>29</v>
+      </c>
+      <c r="E1" t="s" s="1">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="s" s="2">
+        <v>33</v>
+      </c>
+      <c r="B2" t="s" s="2">
+        <v>34</v>
+      </c>
+      <c r="C2" t="s" s="2">
+        <v>34</v>
+      </c>
+      <c r="D2" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="E2" t="s" s="2">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="s" s="2">
+        <v>36</v>
+      </c>
+      <c r="B3" t="s" s="2">
+        <v>37</v>
+      </c>
+      <c r="C3" t="s" s="2">
+        <v>38</v>
+      </c>
+      <c r="D3" t="s" s="2">
+        <v>39</v>
+      </c>
+      <c r="E3" s="2"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="s" s="2">
+        <v>40</v>
+      </c>
+      <c r="B4" t="s" s="2">
+        <v>41</v>
+      </c>
+      <c r="C4" t="s" s="2">
+        <v>38</v>
+      </c>
+      <c r="D4" t="s" s="2">
+        <v>39</v>
+      </c>
+      <c r="E4" s="2"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="s" s="2">
+        <v>42</v>
+      </c>
+      <c r="B5" t="s" s="2">
+        <v>43</v>
+      </c>
+      <c r="C5" t="s" s="2">
+        <v>38</v>
+      </c>
+      <c r="D5" t="s" s="2">
+        <v>39</v>
+      </c>
+      <c r="E5" s="2"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="s" s="2">
+        <v>44</v>
+      </c>
+      <c r="B6" t="s" s="2">
+        <v>45</v>
+      </c>
+      <c r="C6" t="s" s="2">
+        <v>38</v>
+      </c>
+      <c r="D6" t="s" s="2">
+        <v>39</v>
+      </c>
+      <c r="E6" s="2"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="s" s="2">
+        <v>46</v>
+      </c>
+      <c r="B7" t="s" s="2">
+        <v>47</v>
+      </c>
+      <c r="C7" t="s" s="2">
+        <v>38</v>
+      </c>
+      <c r="D7" t="s" s="2">
+        <v>39</v>
+      </c>
+      <c r="E7" s="2"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="s" s="2">
+        <v>48</v>
+      </c>
+      <c r="B8" t="s" s="2">
+        <v>49</v>
+      </c>
+      <c r="C8" t="s" s="2">
+        <v>38</v>
+      </c>
+      <c r="D8" t="s" s="2">
+        <v>39</v>
+      </c>
+      <c r="E8" s="2"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="s" s="2">
+        <v>50</v>
+      </c>
+      <c r="B9" t="s" s="2">
+        <v>51</v>
+      </c>
+      <c r="C9" t="s" s="2">
+        <v>38</v>
+      </c>
+      <c r="D9" t="s" s="2">
+        <v>39</v>
+      </c>
+      <c r="E9" s="2"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="s" s="2">
+        <v>52</v>
+      </c>
+      <c r="B10" t="s" s="2">
+        <v>53</v>
+      </c>
+      <c r="C10" t="s" s="2">
+        <v>38</v>
+      </c>
+      <c r="D10" t="s" s="2">
+        <v>39</v>
+      </c>
+      <c r="E10" s="2"/>
+    </row>
+    <row r="11">
+      <c r="A11" t="s" s="2">
+        <v>54</v>
+      </c>
+      <c r="B11" t="s" s="2">
+        <v>55</v>
+      </c>
+      <c r="C11" t="s" s="2">
+        <v>38</v>
+      </c>
+      <c r="D11" t="s" s="2">
+        <v>39</v>
+      </c>
+      <c r="E11" s="2"/>
+    </row>
+    <row r="12">
+      <c r="A12" t="s" s="2">
+        <v>56</v>
+      </c>
+      <c r="B12" t="s" s="2">
+        <v>57</v>
+      </c>
+      <c r="C12" t="s" s="2">
+        <v>38</v>
+      </c>
+      <c r="D12" t="s" s="2">
+        <v>39</v>
+      </c>
+      <c r="E12" s="2"/>
+    </row>
+    <row r="13">
+      <c r="A13" t="s" s="2">
+        <v>58</v>
+      </c>
+      <c r="B13" t="s" s="2">
+        <v>59</v>
+      </c>
+      <c r="C13" t="s" s="2">
+        <v>38</v>
+      </c>
+      <c r="D13" t="s" s="2">
+        <v>39</v>
+      </c>
+      <c r="E13" s="2"/>
+    </row>
+    <row r="14">
+      <c r="A14" t="s" s="2">
+        <v>60</v>
+      </c>
+      <c r="B14" t="s" s="2">
+        <v>61</v>
+      </c>
+      <c r="C14" t="s" s="2">
+        <v>38</v>
+      </c>
+      <c r="D14" t="s" s="2">
+        <v>39</v>
+      </c>
+      <c r="E14" s="2"/>
+    </row>
+    <row r="15">
+      <c r="A15" t="s" s="2">
+        <v>62</v>
+      </c>
+      <c r="B15" t="s" s="2">
+        <v>63</v>
+      </c>
+      <c r="C15" t="s" s="2">
+        <v>38</v>
+      </c>
+      <c r="D15" t="s" s="2">
+        <v>39</v>
+      </c>
+      <c r="E15" s="2"/>
+    </row>
+    <row r="16">
+      <c r="A16" t="s" s="2">
+        <v>64</v>
+      </c>
+      <c r="B16" t="s" s="2">
+        <v>65</v>
+      </c>
+      <c r="C16" t="s" s="2">
+        <v>38</v>
+      </c>
+      <c r="D16" t="s" s="2">
+        <v>39</v>
+      </c>
+      <c r="E16" s="2"/>
+    </row>
+    <row r="17">
+      <c r="A17" t="s" s="2">
+        <v>66</v>
+      </c>
+      <c r="B17" t="s" s="2">
+        <v>67</v>
+      </c>
+      <c r="C17" t="s" s="2">
+        <v>38</v>
+      </c>
+      <c r="D17" t="s" s="2">
+        <v>39</v>
+      </c>
+      <c r="E17" s="2"/>
+    </row>
+    <row r="18">
+      <c r="A18" t="s" s="2">
+        <v>68</v>
+      </c>
+      <c r="B18" t="s" s="2">
+        <v>69</v>
+      </c>
+      <c r="C18" t="s" s="2">
+        <v>38</v>
+      </c>
+      <c r="D18" t="s" s="2">
+        <v>39</v>
+      </c>
+      <c r="E18" s="2"/>
+    </row>
+    <row r="19">
+      <c r="A19" t="s" s="2">
+        <v>70</v>
+      </c>
+      <c r="B19" t="s" s="2">
+        <v>71</v>
+      </c>
+      <c r="C19" t="s" s="2">
+        <v>38</v>
+      </c>
+      <c r="D19" t="s" s="2">
+        <v>39</v>
+      </c>
+      <c r="E19" s="2"/>
+    </row>
+    <row r="20">
+      <c r="A20" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="B20" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="C20" t="s" s="2">
+        <v>38</v>
+      </c>
+      <c r="D20" t="s" s="2">
+        <v>39</v>
+      </c>
+      <c r="E20" s="2"/>
+    </row>
+    <row r="21">
+      <c r="A21" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="B21" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="C21" t="s" s="2">
+        <v>38</v>
+      </c>
+      <c r="D21" t="s" s="2">
+        <v>39</v>
+      </c>
+      <c r="E21" s="2"/>
+    </row>
+    <row r="22">
+      <c r="A22" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="B22" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="C22" t="s" s="2">
+        <v>38</v>
+      </c>
+      <c r="D22" t="s" s="2">
+        <v>39</v>
+      </c>
+      <c r="E22" s="2"/>
+    </row>
+    <row r="23">
+      <c r="A23" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="B23" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="C23" t="s" s="2">
+        <v>38</v>
+      </c>
+      <c r="D23" t="s" s="2">
+        <v>39</v>
+      </c>
+      <c r="E23" s="2"/>
+    </row>
+    <row r="24">
+      <c r="A24" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="B24" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="C24" t="s" s="2">
+        <v>38</v>
+      </c>
+      <c r="D24" t="s" s="2">
+        <v>39</v>
+      </c>
+      <c r="E24" s="2"/>
+    </row>
+    <row r="25">
+      <c r="A25" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="B25" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="C25" t="s" s="2">
+        <v>38</v>
+      </c>
+      <c r="D25" t="s" s="2">
+        <v>39</v>
+      </c>
+      <c r="E25" s="2"/>
+    </row>
+    <row r="26">
+      <c r="A26" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="B26" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="C26" t="s" s="2">
+        <v>38</v>
+      </c>
+      <c r="D26" t="s" s="2">
+        <v>39</v>
+      </c>
+      <c r="E26" s="2"/>
+    </row>
+    <row r="27">
+      <c r="A27" t="s" s="2">
+        <v>86</v>
+      </c>
+      <c r="B27" t="s" s="2">
+        <v>87</v>
+      </c>
+      <c r="C27" t="s" s="2">
+        <v>38</v>
+      </c>
+      <c r="D27" t="s" s="2">
+        <v>39</v>
+      </c>
+      <c r="E27" s="2"/>
+    </row>
+    <row r="28">
+      <c r="A28" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="B28" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="C28" t="s" s="2">
+        <v>38</v>
+      </c>
+      <c r="D28" t="s" s="2">
+        <v>39</v>
+      </c>
+      <c r="E28" s="2"/>
+    </row>
+    <row r="29">
+      <c r="A29" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="B29" t="s" s="2">
+        <v>91</v>
+      </c>
+      <c r="C29" t="s" s="2">
+        <v>38</v>
+      </c>
+      <c r="D29" t="s" s="2">
+        <v>39</v>
+      </c>
+      <c r="E29" s="2"/>
+    </row>
+    <row r="30">
+      <c r="A30" t="s" s="2">
+        <v>92</v>
+      </c>
+      <c r="B30" t="s" s="2">
+        <v>93</v>
+      </c>
+      <c r="C30" t="s" s="2">
+        <v>38</v>
+      </c>
+      <c r="D30" t="s" s="2">
+        <v>39</v>
+      </c>
+      <c r="E30" s="2"/>
+    </row>
+    <row r="31">
+      <c r="A31" t="s" s="2">
+        <v>94</v>
+      </c>
+      <c r="B31" t="s" s="2">
+        <v>95</v>
+      </c>
+      <c r="C31" t="s" s="2">
+        <v>38</v>
+      </c>
+      <c r="D31" t="s" s="2">
+        <v>39</v>
+      </c>
+      <c r="E31" s="2"/>
+    </row>
+    <row r="32">
+      <c r="A32" t="s" s="2">
+        <v>96</v>
+      </c>
+      <c r="B32" t="s" s="2">
+        <v>97</v>
+      </c>
+      <c r="C32" t="s" s="2">
+        <v>38</v>
+      </c>
+      <c r="D32" t="s" s="2">
+        <v>39</v>
+      </c>
+      <c r="E32" s="2"/>
+    </row>
+    <row r="33">
+      <c r="A33" t="s" s="2">
+        <v>98</v>
+      </c>
+      <c r="B33" t="s" s="2">
+        <v>99</v>
+      </c>
+      <c r="C33" t="s" s="2">
+        <v>38</v>
+      </c>
+      <c r="D33" t="s" s="2">
+        <v>39</v>
+      </c>
+      <c r="E33" s="2"/>
+    </row>
+    <row r="34">
+      <c r="A34" t="s" s="2">
+        <v>100</v>
+      </c>
+      <c r="B34" t="s" s="2">
+        <v>101</v>
+      </c>
+      <c r="C34" t="s" s="2">
+        <v>38</v>
+      </c>
+      <c r="D34" t="s" s="2">
+        <v>39</v>
+      </c>
+      <c r="E34" s="2"/>
+    </row>
+    <row r="35">
+      <c r="A35" t="s" s="2">
+        <v>102</v>
+      </c>
+      <c r="B35" t="s" s="2">
+        <v>103</v>
+      </c>
+      <c r="C35" t="s" s="2">
+        <v>38</v>
+      </c>
+      <c r="D35" t="s" s="2">
+        <v>39</v>
+      </c>
+      <c r="E35" s="2"/>
+    </row>
+    <row r="36">
+      <c r="A36" t="s" s="2">
+        <v>104</v>
+      </c>
+      <c r="B36" t="s" s="2">
+        <v>105</v>
+      </c>
+      <c r="C36" t="s" s="2">
+        <v>38</v>
+      </c>
+      <c r="D36" t="s" s="2">
+        <v>39</v>
+      </c>
+      <c r="E36" s="2"/>
+    </row>
+    <row r="37">
+      <c r="A37" t="s" s="2">
+        <v>106</v>
+      </c>
+      <c r="B37" t="s" s="2">
+        <v>107</v>
+      </c>
+      <c r="C37" t="s" s="2">
+        <v>38</v>
+      </c>
+      <c r="D37" t="s" s="2">
+        <v>39</v>
+      </c>
+      <c r="E37" s="2"/>
+    </row>
+    <row r="38">
+      <c r="A38" t="s" s="2">
+        <v>108</v>
+      </c>
+      <c r="B38" t="s" s="2">
+        <v>109</v>
+      </c>
+      <c r="C38" t="s" s="2">
+        <v>38</v>
+      </c>
+      <c r="D38" t="s" s="2">
+        <v>39</v>
+      </c>
+      <c r="E38" s="2"/>
+    </row>
+    <row r="39">
+      <c r="A39" t="s" s="2">
+        <v>110</v>
+      </c>
+      <c r="B39" t="s" s="2">
+        <v>111</v>
+      </c>
+      <c r="C39" t="s" s="2">
+        <v>38</v>
+      </c>
+      <c r="D39" t="s" s="2">
+        <v>39</v>
+      </c>
+      <c r="E39" s="2"/>
+    </row>
+    <row r="40">
+      <c r="A40" t="s" s="2">
+        <v>112</v>
+      </c>
+      <c r="B40" t="s" s="2">
+        <v>113</v>
+      </c>
+      <c r="C40" t="s" s="2">
+        <v>38</v>
+      </c>
+      <c r="D40" t="s" s="2">
+        <v>39</v>
+      </c>
+      <c r="E40" s="2"/>
+    </row>
+    <row r="41">
+      <c r="A41" t="s" s="2">
+        <v>114</v>
+      </c>
+      <c r="B41" t="s" s="2">
+        <v>115</v>
+      </c>
+      <c r="C41" t="s" s="2">
+        <v>38</v>
+      </c>
+      <c r="D41" t="s" s="2">
+        <v>39</v>
+      </c>
+      <c r="E41" s="2"/>
+    </row>
+    <row r="42">
+      <c r="A42" t="s" s="2">
+        <v>116</v>
+      </c>
+      <c r="B42" t="s" s="2">
+        <v>117</v>
+      </c>
+      <c r="C42" t="s" s="2">
+        <v>38</v>
+      </c>
+      <c r="D42" t="s" s="2">
+        <v>39</v>
+      </c>
+      <c r="E42" s="2"/>
+    </row>
+    <row r="43">
+      <c r="A43" t="s" s="2">
+        <v>118</v>
+      </c>
+      <c r="B43" t="s" s="2">
+        <v>119</v>
+      </c>
+      <c r="C43" t="s" s="2">
+        <v>38</v>
+      </c>
+      <c r="D43" t="s" s="2">
+        <v>39</v>
+      </c>
+      <c r="E43" s="2"/>
+    </row>
+    <row r="44">
+      <c r="A44" t="s" s="2">
+        <v>120</v>
+      </c>
+      <c r="B44" t="s" s="2">
+        <v>121</v>
+      </c>
+      <c r="C44" t="s" s="2">
+        <v>38</v>
+      </c>
+      <c r="D44" t="s" s="2">
+        <v>39</v>
+      </c>
+      <c r="E44" s="2"/>
+    </row>
+    <row r="45">
+      <c r="A45" t="s" s="2">
+        <v>122</v>
+      </c>
+      <c r="B45" t="s" s="2">
+        <v>123</v>
+      </c>
+      <c r="C45" t="s" s="2">
+        <v>38</v>
+      </c>
+      <c r="D45" t="s" s="2">
+        <v>39</v>
+      </c>
+      <c r="E45" s="2"/>
+    </row>
+    <row r="46">
+      <c r="A46" t="s" s="2">
+        <v>124</v>
+      </c>
+      <c r="B46" t="s" s="2">
+        <v>125</v>
+      </c>
+      <c r="C46" t="s" s="2">
+        <v>38</v>
+      </c>
+      <c r="D46" t="s" s="2">
+        <v>39</v>
+      </c>
+      <c r="E46" s="2"/>
+    </row>
+    <row r="47">
+      <c r="A47" t="s" s="2">
+        <v>126</v>
+      </c>
+      <c r="B47" t="s" s="2">
+        <v>127</v>
+      </c>
+      <c r="C47" t="s" s="2">
+        <v>38</v>
+      </c>
+      <c r="D47" t="s" s="2">
+        <v>39</v>
+      </c>
+      <c r="E47" s="2"/>
+    </row>
+    <row r="48">
+      <c r="A48" t="s" s="2">
+        <v>128</v>
+      </c>
+      <c r="B48" t="s" s="2">
+        <v>129</v>
+      </c>
+      <c r="C48" t="s" s="2">
+        <v>38</v>
+      </c>
+      <c r="D48" t="s" s="2">
+        <v>39</v>
+      </c>
+      <c r="E48" s="2"/>
+    </row>
+  </sheetData>
+  <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <dimension ref="A1:E3"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <sheetData>
@@ -428,7 +1445,7 @@
     </row>
     <row r="2">
       <c r="A2" t="s" s="2">
-        <v>33</v>
+        <v>130</v>
       </c>
       <c r="B2" t="s" s="2">
         <v>34</v>
@@ -445,16 +1462,16 @@
     </row>
     <row r="3">
       <c r="A3" t="s" s="2">
-        <v>36</v>
+        <v>131</v>
       </c>
       <c r="B3" t="s" s="2">
-        <v>37</v>
+        <v>132</v>
       </c>
       <c r="C3" t="s" s="2">
         <v>38</v>
       </c>
       <c r="D3" t="s" s="2">
-        <v>39</v>
+        <v>133</v>
       </c>
       <c r="E3" s="2"/>
     </row>

--- a/ig/ch-elm/ch-elm-results-geno-to-component-interpretation-code.xlsx
+++ b/ig/ch-elm/ch-elm-results-geno-to-component-interpretation-code.xlsx
@@ -31,7 +31,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.15.0</t>
+    <t>1.15.1</t>
   </si>
   <si>
     <t>Name</t>
@@ -61,7 +61,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-12T07:20:00+00:00</t>
+    <t>2026-08-14T07:34:39+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
